--- a/sim_proj_updated/water_quality_index.xlsx
+++ b/sim_proj_updated/water_quality_index.xlsx
@@ -13,63 +13,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="156" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="117" uniqueCount="24">
   <si>
     <t>Month</t>
   </si>
   <si>
-    <t>كانون الثاني-2022</t>
-  </si>
-  <si>
-    <t>شباط-2022</t>
-  </si>
-  <si>
-    <t>اذار - 2022</t>
-  </si>
-  <si>
-    <t>نيسان - 2022</t>
-  </si>
-  <si>
-    <t>ايار - 2022</t>
-  </si>
-  <si>
-    <t>حزيران - 2022</t>
-  </si>
-  <si>
-    <t>تموز - 2022</t>
-  </si>
-  <si>
-    <t>اب - 2022</t>
-  </si>
-  <si>
-    <t>ايلول - 2022</t>
-  </si>
-  <si>
-    <t>تشرين الاول - 2022</t>
-  </si>
-  <si>
-    <t>تشرين الثاني - 2022</t>
-  </si>
-  <si>
-    <t>كانون الاول - 2022</t>
-  </si>
-  <si>
-    <t>كانون الثاني - 2023</t>
-  </si>
-  <si>
-    <t>شباط - 2023</t>
-  </si>
-  <si>
-    <t>اذار - 2023</t>
-  </si>
-  <si>
-    <t>نيسان - 2023</t>
-  </si>
-  <si>
-    <t>ايار - 2023</t>
-  </si>
-  <si>
-    <t>حزيران - 2023</t>
+    <t>Jan-2022</t>
+  </si>
+  <si>
+    <t>Feb-2022</t>
+  </si>
+  <si>
+    <t>Mar-2022</t>
+  </si>
+  <si>
+    <t>Apr-2022</t>
+  </si>
+  <si>
+    <t>May-2022</t>
+  </si>
+  <si>
+    <t>Jun-2022</t>
+  </si>
+  <si>
+    <t>Jul-2022</t>
+  </si>
+  <si>
+    <t>Aug-2022</t>
+  </si>
+  <si>
+    <t>Sep-2022</t>
+  </si>
+  <si>
+    <t>Oct-2022</t>
+  </si>
+  <si>
+    <t>Nov-2022</t>
+  </si>
+  <si>
+    <t>Dec-2022</t>
+  </si>
+  <si>
+    <t>Jan-2023</t>
+  </si>
+  <si>
+    <t>Feb-2023</t>
+  </si>
+  <si>
+    <t>Mar-2023</t>
+  </si>
+  <si>
+    <t>Apr-2023</t>
+  </si>
+  <si>
+    <t>May-2023</t>
+  </si>
+  <si>
+    <t>Jun-2023</t>
   </si>
   <si>
     <t>WQI</t>
@@ -133,7 +133,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.5703125" customWidth="true"/>
     <col min="2" max="2" width="11.7109375" customWidth="true"/>
     <col min="3" max="3" width="9.28515625" customWidth="true"/>
   </cols>
@@ -154,7 +154,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>51.696786078927502</v>
+        <v>51.326691545603992</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>21</v>
@@ -165,7 +165,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>66.514249567186042</v>
+        <v>66.126016260162615</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>21</v>
@@ -176,10 +176,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>100.04615350468325</v>
+        <v>99.700088853347552</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -187,7 +187,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>71.885004661073367</v>
+        <v>71.606624017059829</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>21</v>
@@ -198,7 +198,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>91.433402139654632</v>
+        <v>91.056459638366874</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>21</v>
@@ -209,7 +209,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>114.7379588937719</v>
+        <v>114.32111599804523</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>22</v>
@@ -220,7 +220,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>92.162085497403112</v>
+        <v>91.861775289884065</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>21</v>
@@ -231,7 +231,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>69.522710525147588</v>
+        <v>69.249637922608741</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>21</v>
@@ -242,7 +242,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>107.81353043015045</v>
+        <v>107.59434892709584</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>22</v>
@@ -253,7 +253,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>84.082736272029109</v>
+        <v>83.89231862810432</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>21</v>
@@ -264,7 +264,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>47.767869667510105</v>
+        <v>47.505229019503318</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>23</v>
@@ -275,7 +275,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>89.524703688906641</v>
+        <v>89.246034919365599</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>21</v>
@@ -286,7 +286,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>54.061936786966726</v>
+        <v>53.833837576080683</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>21</v>
@@ -297,7 +297,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>52.447707195809457</v>
+        <v>52.079412679372702</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>21</v>
@@ -308,7 +308,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>85.519256891729924</v>
+        <v>85.186045581767303</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>21</v>
@@ -319,7 +319,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>72.93707550938872</v>
+        <v>72.659536185525795</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>21</v>
@@ -330,7 +330,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>65.005579970701817</v>
+        <v>64.705864320938304</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>21</v>
@@ -341,7 +341,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>69.58364851067607</v>
+        <v>69.282315962503901</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>21</v>
